--- a/workbooks/methodology/cost_env_collinearity.xlsx
+++ b/workbooks/methodology/cost_env_collinearity.xlsx
@@ -468,13 +468,13 @@
         <v>285</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9335</v>
+        <v>0.9502</v>
       </c>
       <c r="E2" t="n">
-        <v>85.40000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>11.2</v>
+        <v>9.5</v>
       </c>
       <c r="G2" t="n">
         <v>0.65</v>
@@ -501,7 +501,7 @@
         <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>27.6</v>
+        <v>21</v>
       </c>
       <c r="G3" t="n">
         <v>0.65</v>
@@ -522,13 +522,13 @@
         <v>100</v>
       </c>
       <c r="D4" t="n">
-        <v>0.6463</v>
+        <v>0.7658</v>
       </c>
       <c r="E4" t="n">
-        <v>29.3</v>
+        <v>29.8</v>
       </c>
       <c r="F4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
         <v>0.65</v>
@@ -555,7 +555,7 @@
         <v>95</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
         <v>0.65</v>
